--- a/data/delivery_zones.xlsx
+++ b/data/delivery_zones.xlsx
@@ -587,7 +587,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -609,7 +609,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -653,7 +653,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>15</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -719,7 +719,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -741,7 +741,7 @@
         <v>15</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -763,7 +763,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -785,7 +785,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -807,7 +807,7 @@
         <v>20</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -829,7 +829,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -851,7 +851,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -873,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
